--- a/tame_output/ON/bt/strategyON_20231103.xlsx
+++ b/tame_output/ON/bt/strategyON_20231103.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>83.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,17 +1235,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1769"/>
+  <dimension ref="A1:G1770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.094867527064018</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42213,6 +42213,29 @@
       </c>
       <c r="G1769" t="n">
         <v>4.348625204900422</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="2" t="n">
+        <v>45232</v>
+      </c>
+      <c r="B1770" t="n">
+        <v>3.066955604001347</v>
+      </c>
+      <c r="C1770" t="n">
+        <v>3.048277258176837</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>1.550626961539412</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>3.668171618478855</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>2.17442938323927</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>4.352934888120401</v>
       </c>
     </row>
   </sheetData>
